--- a/backend/service/printer-config.xlsx
+++ b/backend/service/printer-config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kinross-my.sharepoint.com/personal/riqborges_kinross_com/Documents/Documentos/projetos/MoveX/backend/service/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{1B1DE19C-37D1-463A-811E-311F800E7560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51643614-7F72-4093-9128-ADC12764A37E}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{1B1DE19C-37D1-463A-811E-311F800E7560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33FB60EE-FF31-4D6C-B926-258A438E23A2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{83CCA03F-B68E-44EE-B017-FB74DCFD85AB}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{83CCA03F-B68E-44EE-B017-FB74DCFD85AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Nome</t>
   </si>
@@ -75,6 +75,15 @@
   </si>
   <si>
     <t>10.205.69.9</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>9075DE0A1D6B</t>
+  </si>
+  <si>
+    <t>9075DE0A1D67</t>
   </si>
 </sst>
 </file>
@@ -116,7 +125,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -133,6 +143,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -452,59 +466,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E13510AD-22AF-43CE-9EEB-A2D490CAECDE}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
+      <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
+      <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
+      <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
